--- a/hac_project/Input_datahall.xlsx
+++ b/hac_project/Input_datahall.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\preytocladue\hac_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{00C445DC-BA47-43EE-A86B-DCEF9C0B2F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB1743D6-E1A4-4C79-B53F-BA740759E5F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{D0570127-1DD5-4E28-A8A7-AAA65C87DED7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{D0570127-1DD5-4E28-A8A7-AAA65C87DED7}"/>
   </bookViews>
   <sheets>
     <sheet name="Example" sheetId="1" r:id="rId1"/>
     <sheet name="Example (2)" sheetId="3" r:id="rId2"/>
+    <sheet name="Example (3)" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="10">
   <si>
     <t>HAC1</t>
   </si>
@@ -913,4 +914,234 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E912BF3-6D01-4D16-BDAE-645F15267044}">
+  <dimension ref="A1:L16"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.09765625" customWidth="1"/>
+    <col min="2" max="2" width="11.796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>20</v>
+      </c>
+      <c r="D2">
+        <v>20</v>
+      </c>
+      <c r="E2">
+        <v>20</v>
+      </c>
+      <c r="F2">
+        <v>20</v>
+      </c>
+      <c r="G2">
+        <v>20</v>
+      </c>
+      <c r="H2">
+        <v>20</v>
+      </c>
+      <c r="I2">
+        <v>20</v>
+      </c>
+      <c r="J2">
+        <v>20</v>
+      </c>
+      <c r="K2">
+        <v>20</v>
+      </c>
+      <c r="L2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>20</v>
+      </c>
+      <c r="D3">
+        <v>20</v>
+      </c>
+      <c r="E3">
+        <v>20</v>
+      </c>
+      <c r="F3">
+        <v>20</v>
+      </c>
+      <c r="G3">
+        <v>20</v>
+      </c>
+      <c r="H3">
+        <v>20</v>
+      </c>
+      <c r="I3">
+        <v>20</v>
+      </c>
+      <c r="J3">
+        <v>20</v>
+      </c>
+      <c r="K3">
+        <v>20</v>
+      </c>
+      <c r="L3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>20</v>
+      </c>
+      <c r="D4">
+        <v>150</v>
+      </c>
+      <c r="E4">
+        <v>150</v>
+      </c>
+      <c r="F4">
+        <v>150</v>
+      </c>
+      <c r="G4">
+        <v>150</v>
+      </c>
+      <c r="H4">
+        <v>150</v>
+      </c>
+      <c r="I4">
+        <v>150</v>
+      </c>
+      <c r="J4">
+        <v>150</v>
+      </c>
+      <c r="K4">
+        <v>20</v>
+      </c>
+      <c r="L4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>20</v>
+      </c>
+      <c r="D5">
+        <v>150</v>
+      </c>
+      <c r="E5">
+        <v>150</v>
+      </c>
+      <c r="F5">
+        <v>150</v>
+      </c>
+      <c r="G5">
+        <v>150</v>
+      </c>
+      <c r="H5">
+        <v>150</v>
+      </c>
+      <c r="I5">
+        <v>150</v>
+      </c>
+      <c r="J5">
+        <v>150</v>
+      </c>
+      <c r="K5">
+        <v>20</v>
+      </c>
+      <c r="L5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>150</v>
+      </c>
+      <c r="E6">
+        <v>150</v>
+      </c>
+      <c r="F6">
+        <v>150</v>
+      </c>
+      <c r="G6">
+        <v>150</v>
+      </c>
+      <c r="H6">
+        <v>150</v>
+      </c>
+      <c r="I6">
+        <v>150</v>
+      </c>
+      <c r="J6">
+        <v>150</v>
+      </c>
+      <c r="K6">
+        <v>20</v>
+      </c>
+      <c r="L6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B6" xr:uid="{447FDD3D-393A-4092-9E1E-AD4640F89665}">
+      <formula1>$A$15:$A$16</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>